--- a/#Innovation_anonymized.xlsx
+++ b/#Innovation_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
